--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3589,6 +3589,135 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118098657</v>
+      </c>
+      <c r="B25" t="n">
+        <v>44523</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>102018</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Zygaena lonicerae</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stadshajden, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>701186</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6391366</v>
+      </c>
+      <c r="S25" t="n">
+        <v>11</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Peter Olofsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Peter Olofsson, Evelina Lindgren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1415,60 +1415,52 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56212174</v>
+        <v>56514313</v>
       </c>
       <c r="B8" t="n">
-        <v>88856</v>
+        <v>89170</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2008</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ölbäck, Gtl</t>
+          <t>Ölbäck NR, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701171.6356824719</v>
+        <v>701191.4179363601</v>
       </c>
       <c r="R8" t="n">
-        <v>6391403.833949611</v>
+        <v>6391395.160483933</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1495,7 +1487,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-12-22</t>
+          <t>2016-01-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1505,12 +1497,17 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-12-22</t>
+          <t>2016-01-14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Frystorkade</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,67 +1523,75 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Törnvall</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Törnvall</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>56514313</v>
+        <v>67978565</v>
       </c>
       <c r="B9" t="n">
-        <v>89170</v>
+        <v>88904</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>5735</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Ramaria broomei</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Cotton &amp; Wakef.) R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ölbäck NR, Gtl</t>
+          <t>Endre, Ölbäck, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701191.4179363601</v>
+        <v>701161.6256615464</v>
       </c>
       <c r="R9" t="n">
-        <v>6391395.160483933</v>
+        <v>6391378.121156982</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1610,7 +1615,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2016-01-14</t>
+          <t>2017-10-16</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1620,17 +1625,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2016-01-14</t>
+          <t>2017-10-16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Frystorkade</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1651,17 +1651,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Dennis Nyström, Magnus Martinsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67978565</v>
+        <v>96781508</v>
       </c>
       <c r="B10" t="n">
-        <v>88904</v>
+        <v>42591</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1670,51 +1670,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5735</v>
+        <v>101260</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria broomei</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Cotton &amp; Wakef.) R.H.Petersen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Endre, Ölbäck, Gtl</t>
+          <t>Ölbäck NR, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701161.6256615464</v>
+        <v>701243.8970059552</v>
       </c>
       <c r="R10" t="n">
-        <v>6391378.121156982</v>
+        <v>6391355.923005602</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1738,7 +1741,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2017-10-16</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1748,7 +1751,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2017-10-16</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1769,22 +1772,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Dennis Nyström, Magnus Martinsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96781508</v>
+        <v>97934797</v>
       </c>
       <c r="B11" t="n">
-        <v>42591</v>
+        <v>88852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1793,40 +1800,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101260</v>
+        <v>4191</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1834,13 +1839,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701243.8970059552</v>
+        <v>701191.4179363601</v>
       </c>
       <c r="R11" t="n">
-        <v>6391355.923005602</v>
+        <v>6391395.160483933</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1864,7 +1869,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1874,7 +1879,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1892,29 +1897,30 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97934797</v>
+        <v>103581468</v>
       </c>
       <c r="B12" t="n">
-        <v>88852</v>
+        <v>44330</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1923,25 +1929,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4191</v>
+        <v>102018</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1949,26 +1955,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ölbäck NR, Gtl</t>
+          <t>Ölbäck, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701191.4179363601</v>
+        <v>701184.031727773</v>
       </c>
       <c r="R12" t="n">
-        <v>6391395.160483933</v>
+        <v>6391359.921051381</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1992,7 +2000,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2022-07-09</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2002,7 +2010,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2022-07-09</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2020,30 +2028,25 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103581468</v>
+        <v>105107550</v>
       </c>
       <c r="B13" t="n">
-        <v>44330</v>
+        <v>104510</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2056,50 +2059,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102018</v>
+        <v>1124</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Timjansnyltrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Orobanche alba</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>Stephan ex Willd.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ölbäck, Gtl</t>
+          <t>Ölbäck, V infartskörväg i SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701184.031727773</v>
+        <v>701221.7953813276</v>
       </c>
       <c r="R13" t="n">
-        <v>6391359.921051381</v>
+        <v>6391400.426241548</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2123,7 +2122,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
+          <t>2009-07-15</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2133,7 +2132,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
+          <t>2009-07-15</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2147,26 +2146,34 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Grusgrop i S</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105107550</v>
+        <v>105107597</v>
       </c>
       <c r="B14" t="n">
         <v>104510</v>
@@ -2211,14 +2218,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ölbäck, V infartskörväg i SV-del, Gtl</t>
+          <t>Ölbäck, ladvägen SV, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701221.7953813276</v>
+        <v>701244.0034554653</v>
       </c>
       <c r="R14" t="n">
-        <v>6391400.426241548</v>
+        <v>6391353.782299309</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2274,7 +2281,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Grusgrop i S</t>
+          <t>Åsrygg, SO-kant</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2296,7 +2303,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105107597</v>
+        <v>105107568</v>
       </c>
       <c r="B15" t="n">
         <v>104510</v>
@@ -2331,7 +2338,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2345,10 +2352,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701244.0034554653</v>
+        <v>701245.7304084217</v>
       </c>
       <c r="R15" t="n">
-        <v>6391353.782299309</v>
+        <v>6391383.9120681</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2391,6 +2398,11 @@
       <c r="AB15" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Summa 2108 ex på hela Ölbäck</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2426,7 +2438,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105107568</v>
+        <v>105107588</v>
       </c>
       <c r="B16" t="n">
         <v>104510</v>
@@ -2461,7 +2473,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2471,14 +2483,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ölbäck, ladvägen SV, Gtl</t>
+          <t>Ölbäck, V infartskörväg i SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701245.7304084217</v>
+        <v>701185.7242880682</v>
       </c>
       <c r="R16" t="n">
-        <v>6391383.9120681</v>
+        <v>6391369.125652875</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2523,11 +2535,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Summa 2108 ex på hela Ölbäck</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2539,7 +2546,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Åsrygg, SO-kant</t>
+          <t>Torräng vid körväg</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2561,7 +2568,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105107588</v>
+        <v>105107615</v>
       </c>
       <c r="B17" t="n">
         <v>104510</v>
@@ -2596,7 +2603,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2606,14 +2613,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ölbäck, V infartskörväg i SV-del, Gtl</t>
+          <t>Ölbäck 200 m SSV, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701185.7242880682</v>
+        <v>701229.54836096</v>
       </c>
       <c r="R17" t="n">
-        <v>6391369.125652875</v>
+        <v>6391341.797012418</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2640,7 +2647,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2009-07-15</t>
+          <t>1998-07-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2650,7 +2657,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2009-07-15</t>
+          <t>1998-07-14</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2669,7 +2676,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Torräng vid körväg</t>
+          <t>Grusås vid körväg.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2691,7 +2698,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105107615</v>
+        <v>105107570</v>
       </c>
       <c r="B18" t="n">
         <v>104510</v>
@@ -2726,7 +2733,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2736,14 +2743,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ölbäck 200 m SSV, Gtl</t>
+          <t>Ölbäck, V infartskörväg i SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701229.54836096</v>
+        <v>701238.8395503648</v>
       </c>
       <c r="R18" t="n">
-        <v>6391341.797012418</v>
+        <v>6391381.959921784</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2770,7 +2777,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>1998-07-14</t>
+          <t>2009-07-15</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2780,7 +2787,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1998-07-14</t>
+          <t>2009-07-15</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2788,6 +2795,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>mot SV frän skyltställ i grusgrop</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2799,7 +2811,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Grusås vid körväg.</t>
+          <t>Körväg och torrbackar</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2821,7 +2833,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>105107570</v>
+        <v>105107572</v>
       </c>
       <c r="B19" t="n">
         <v>104510</v>
@@ -2856,7 +2868,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2870,10 +2882,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701238.8395503648</v>
+        <v>701204.7085225175</v>
       </c>
       <c r="R19" t="n">
-        <v>6391381.959921784</v>
+        <v>6391376.507408389</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2918,11 +2930,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>mot SV frän skyltställ i grusgrop</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2934,7 +2941,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Körväg och torrbackar</t>
+          <t>Torrbacke på åsrygg S-del</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2956,7 +2963,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105107572</v>
+        <v>105107593</v>
       </c>
       <c r="B20" t="n">
         <v>104510</v>
@@ -2991,7 +2998,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3001,14 +3008,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ölbäck, V infartskörväg i SV-del, Gtl</t>
+          <t>Ölbäck, ladvägen SV, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701204.7085225175</v>
+        <v>701246.8215304908</v>
       </c>
       <c r="R20" t="n">
-        <v>6391376.507408389</v>
+        <v>6391361.969926095</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3064,7 +3071,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Torrbacke på åsrygg S-del</t>
+          <t>Åsrygg, SO-kant</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3086,7 +3093,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>105107593</v>
+        <v>105107634</v>
       </c>
       <c r="B21" t="n">
         <v>104510</v>
@@ -3121,7 +3128,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3131,14 +3138,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ölbäck, ladvägen SV, Gtl</t>
+          <t>Ölbäck 350 m SSV, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701246.8215304908</v>
+        <v>701229.5177455944</v>
       </c>
       <c r="R21" t="n">
-        <v>6391361.969926095</v>
+        <v>6391331.601950945</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3165,7 +3172,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2009-07-15</t>
+          <t>1994-08-08</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3175,7 +3182,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2009-07-15</t>
+          <t>1994-08-08</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3183,6 +3190,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ca 40 ex. Tidigare känd lokal.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3194,7 +3206,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Åsrygg, SO-kant</t>
+          <t>Torrbacke.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3216,7 +3228,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>105107634</v>
+        <v>106605053</v>
       </c>
       <c r="B22" t="n">
         <v>104510</v>
@@ -3249,26 +3261,17 @@
           <t>Stephan ex Willd.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ölbäck 350 m SSV, Gtl</t>
+          <t>Ölbäck, ca 300 m SSV P-plats, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>701229.5177455944</v>
+        <v>701209.62460842</v>
       </c>
       <c r="R22" t="n">
-        <v>6391331.601950945</v>
+        <v>6391331.685870692</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3295,7 +3298,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>1994-08-08</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3305,7 +3308,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1994-08-08</t>
+          <t>1992-12-31</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3313,11 +3316,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ca 40 ex. Tidigare känd lokal.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3326,11 +3324,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Torrbacke.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3340,7 +3333,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Torgny Rosvall</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3351,10 +3344,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>106605053</v>
+        <v>106643595</v>
       </c>
       <c r="B23" t="n">
-        <v>104510</v>
+        <v>88856</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3367,34 +3360,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1124</v>
+        <v>2008</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Timjansnyltrot</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Orobanche alba</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Stephan ex Willd.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ölbäck, ca 300 m SSV P-plats, Gtl</t>
+          <t>Endre, Ölbäck, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>701209.62460842</v>
+        <v>701161.6256615464</v>
       </c>
       <c r="R23" t="n">
-        <v>6391331.685870692</v>
+        <v>6391378.121156982</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3421,7 +3425,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3431,7 +3435,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1992-12-31</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3445,32 +3449,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Torgny Rosvall</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>106643595</v>
+        <v>118098657</v>
       </c>
       <c r="B24" t="n">
-        <v>88856</v>
+        <v>44525</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3483,48 +3484,54 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2008</v>
+        <v>102018</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Endre, Ölbäck, Gtl</t>
+          <t>Stadshajden, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>701161.6256615464</v>
+        <v>701186</v>
       </c>
       <c r="R24" t="n">
-        <v>6391378.121156982</v>
+        <v>6391366</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3548,22 +3555,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-02-02</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-02-02</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3572,29 +3579,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Peter Olofsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Peter Olofsson, Evelina Lindgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118098657</v>
+        <v>120661706</v>
       </c>
       <c r="B25" t="n">
-        <v>44525</v>
+        <v>86174</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3603,58 +3609,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102018</v>
+        <v>248956</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stadshajden, Gtl</t>
+          <t>Stadshajden, Stadshajden, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>701186</v>
+        <v>701191</v>
       </c>
       <c r="R25" t="n">
-        <v>6391366</v>
+        <v>6391369</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3678,22 +3667,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3708,22 +3687,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Peter Olofsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Peter Olofsson, Evelina Lindgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120661706</v>
+        <v>120661712</v>
       </c>
       <c r="B26" t="n">
-        <v>86174</v>
+        <v>89329</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3732,25 +3711,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>248956</v>
+        <v>245042</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3760,10 +3739,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>701191</v>
+        <v>701227</v>
       </c>
       <c r="R26" t="n">
-        <v>6391369</v>
+        <v>6391428</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3819,108 +3798,6 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>120661712</v>
-      </c>
-      <c r="B27" t="n">
-        <v>89329</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>245042</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Besk kastanjemusseron</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Tricholoma batschii</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Stadshajden, Stadshajden, Gtl</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>701227</v>
-      </c>
-      <c r="R27" t="n">
-        <v>6391428</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Endre</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2024-10-25</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2024-10-25</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -2046,12 +2046,7 @@
         <v>105107550</v>
       </c>
       <c r="B13" t="n">
-        <v>104510</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106990</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2092,10 +2087,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701221.7953813276</v>
+        <v>701222</v>
       </c>
       <c r="R13" t="n">
-        <v>6391400.426241548</v>
+        <v>6391400</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2125,19 +2120,9 @@
           <t>2009-07-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2009-07-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2176,12 +2161,7 @@
         <v>105107597</v>
       </c>
       <c r="B14" t="n">
-        <v>104510</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106990</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2222,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701244.0034554653</v>
+        <v>701244</v>
       </c>
       <c r="R14" t="n">
-        <v>6391353.782299309</v>
+        <v>6391354</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2255,19 +2235,9 @@
           <t>2009-07-15</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2009-07-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2306,12 +2276,7 @@
         <v>105107568</v>
       </c>
       <c r="B15" t="n">
-        <v>104510</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106990</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2352,10 +2317,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701245.7304084217</v>
+        <v>701246</v>
       </c>
       <c r="R15" t="n">
-        <v>6391383.9120681</v>
+        <v>6391384</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2385,19 +2350,9 @@
           <t>2009-07-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2009-07-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2441,12 +2396,7 @@
         <v>105107588</v>
       </c>
       <c r="B16" t="n">
-        <v>104510</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106990</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2487,10 +2437,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701185.7242880682</v>
+        <v>701186</v>
       </c>
       <c r="R16" t="n">
-        <v>6391369.125652875</v>
+        <v>6391369</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2520,19 +2470,9 @@
           <t>2009-07-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2009-07-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2571,12 +2511,7 @@
         <v>105107615</v>
       </c>
       <c r="B17" t="n">
-        <v>104510</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106990</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2617,10 +2552,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701229.54836096</v>
+        <v>701230</v>
       </c>
       <c r="R17" t="n">
-        <v>6391341.797012418</v>
+        <v>6391342</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2650,19 +2585,9 @@
           <t>1998-07-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>1998-07-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2701,12 +2626,7 @@
         <v>105107570</v>
       </c>
       <c r="B18" t="n">
-        <v>104510</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106990</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2747,10 +2667,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701238.8395503648</v>
+        <v>701239</v>
       </c>
       <c r="R18" t="n">
-        <v>6391381.959921784</v>
+        <v>6391382</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2780,19 +2700,9 @@
           <t>2009-07-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2009-07-15</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2836,12 +2746,7 @@
         <v>105107572</v>
       </c>
       <c r="B19" t="n">
-        <v>104510</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106990</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2882,10 +2787,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701204.7085225175</v>
+        <v>701205</v>
       </c>
       <c r="R19" t="n">
-        <v>6391376.507408389</v>
+        <v>6391377</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2915,19 +2820,9 @@
           <t>2009-07-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2009-07-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2966,12 +2861,7 @@
         <v>105107593</v>
       </c>
       <c r="B20" t="n">
-        <v>104510</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106990</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3012,10 +2902,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701246.8215304908</v>
+        <v>701247</v>
       </c>
       <c r="R20" t="n">
-        <v>6391361.969926095</v>
+        <v>6391362</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3045,19 +2935,9 @@
           <t>2009-07-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2009-07-15</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3096,12 +2976,7 @@
         <v>105107634</v>
       </c>
       <c r="B21" t="n">
-        <v>104510</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106990</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3142,10 +3017,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701229.5177455944</v>
+        <v>701230</v>
       </c>
       <c r="R21" t="n">
-        <v>6391331.601950945</v>
+        <v>6391332</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3175,19 +3050,9 @@
           <t>1994-08-08</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>1994-08-08</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3231,12 +3096,7 @@
         <v>106605053</v>
       </c>
       <c r="B22" t="n">
-        <v>104510</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106990</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3268,10 +3128,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>701209.62460842</v>
+        <v>701210</v>
       </c>
       <c r="R22" t="n">
-        <v>6391331.685870692</v>
+        <v>6391332</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3301,19 +3161,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>1992-12-31</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -2046,7 +2046,7 @@
         <v>105107550</v>
       </c>
       <c r="B13" t="n">
-        <v>106990</v>
+        <v>106999</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>105107597</v>
       </c>
       <c r="B14" t="n">
-        <v>106990</v>
+        <v>106999</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>105107568</v>
       </c>
       <c r="B15" t="n">
-        <v>106990</v>
+        <v>106999</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>105107588</v>
       </c>
       <c r="B16" t="n">
-        <v>106990</v>
+        <v>106999</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>105107615</v>
       </c>
       <c r="B17" t="n">
-        <v>106990</v>
+        <v>106999</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>105107570</v>
       </c>
       <c r="B18" t="n">
-        <v>106990</v>
+        <v>106999</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>105107572</v>
       </c>
       <c r="B19" t="n">
-        <v>106990</v>
+        <v>106999</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>105107593</v>
       </c>
       <c r="B20" t="n">
-        <v>106990</v>
+        <v>106999</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>105107634</v>
       </c>
       <c r="B21" t="n">
-        <v>106990</v>
+        <v>106999</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>106605053</v>
       </c>
       <c r="B22" t="n">
-        <v>106990</v>
+        <v>106999</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -2046,7 +2046,7 @@
         <v>105107550</v>
       </c>
       <c r="B13" t="n">
-        <v>106999</v>
+        <v>107011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>105107597</v>
       </c>
       <c r="B14" t="n">
-        <v>106999</v>
+        <v>107011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>105107568</v>
       </c>
       <c r="B15" t="n">
-        <v>106999</v>
+        <v>107011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>105107588</v>
       </c>
       <c r="B16" t="n">
-        <v>106999</v>
+        <v>107011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>105107615</v>
       </c>
       <c r="B17" t="n">
-        <v>106999</v>
+        <v>107011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>105107570</v>
       </c>
       <c r="B18" t="n">
-        <v>106999</v>
+        <v>107011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>105107572</v>
       </c>
       <c r="B19" t="n">
-        <v>106999</v>
+        <v>107011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>105107593</v>
       </c>
       <c r="B20" t="n">
-        <v>106999</v>
+        <v>107011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>105107634</v>
       </c>
       <c r="B21" t="n">
-        <v>106999</v>
+        <v>107011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>106605053</v>
       </c>
       <c r="B22" t="n">
-        <v>106999</v>
+        <v>107011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -2046,7 +2046,7 @@
         <v>105107550</v>
       </c>
       <c r="B13" t="n">
-        <v>107011</v>
+        <v>107020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>105107597</v>
       </c>
       <c r="B14" t="n">
-        <v>107011</v>
+        <v>107020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>105107568</v>
       </c>
       <c r="B15" t="n">
-        <v>107011</v>
+        <v>107020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>105107588</v>
       </c>
       <c r="B16" t="n">
-        <v>107011</v>
+        <v>107020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>105107615</v>
       </c>
       <c r="B17" t="n">
-        <v>107011</v>
+        <v>107020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>105107570</v>
       </c>
       <c r="B18" t="n">
-        <v>107011</v>
+        <v>107020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>105107572</v>
       </c>
       <c r="B19" t="n">
-        <v>107011</v>
+        <v>107020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>105107593</v>
       </c>
       <c r="B20" t="n">
-        <v>107011</v>
+        <v>107020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>105107634</v>
       </c>
       <c r="B21" t="n">
-        <v>107011</v>
+        <v>107020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>106605053</v>
       </c>
       <c r="B22" t="n">
-        <v>107011</v>
+        <v>107020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -2046,7 +2046,7 @@
         <v>105107550</v>
       </c>
       <c r="B13" t="n">
-        <v>107020</v>
+        <v>107025</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>105107597</v>
       </c>
       <c r="B14" t="n">
-        <v>107020</v>
+        <v>107025</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>105107568</v>
       </c>
       <c r="B15" t="n">
-        <v>107020</v>
+        <v>107025</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>105107588</v>
       </c>
       <c r="B16" t="n">
-        <v>107020</v>
+        <v>107025</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>105107615</v>
       </c>
       <c r="B17" t="n">
-        <v>107020</v>
+        <v>107025</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>105107570</v>
       </c>
       <c r="B18" t="n">
-        <v>107020</v>
+        <v>107025</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>105107572</v>
       </c>
       <c r="B19" t="n">
-        <v>107020</v>
+        <v>107025</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>105107593</v>
       </c>
       <c r="B20" t="n">
-        <v>107020</v>
+        <v>107025</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>105107634</v>
       </c>
       <c r="B21" t="n">
-        <v>107020</v>
+        <v>107025</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>106605053</v>
       </c>
       <c r="B22" t="n">
-        <v>107020</v>
+        <v>107025</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -2046,7 +2046,7 @@
         <v>105107550</v>
       </c>
       <c r="B13" t="n">
-        <v>107025</v>
+        <v>107053</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>105107597</v>
       </c>
       <c r="B14" t="n">
-        <v>107025</v>
+        <v>107053</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>105107568</v>
       </c>
       <c r="B15" t="n">
-        <v>107025</v>
+        <v>107053</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>105107588</v>
       </c>
       <c r="B16" t="n">
-        <v>107025</v>
+        <v>107053</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>105107615</v>
       </c>
       <c r="B17" t="n">
-        <v>107025</v>
+        <v>107053</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>105107570</v>
       </c>
       <c r="B18" t="n">
-        <v>107025</v>
+        <v>107053</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>105107572</v>
       </c>
       <c r="B19" t="n">
-        <v>107025</v>
+        <v>107053</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>105107593</v>
       </c>
       <c r="B20" t="n">
-        <v>107025</v>
+        <v>107053</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>105107634</v>
       </c>
       <c r="B21" t="n">
-        <v>107025</v>
+        <v>107053</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>106605053</v>
       </c>
       <c r="B22" t="n">
-        <v>107025</v>
+        <v>107053</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -2046,7 +2046,7 @@
         <v>105107550</v>
       </c>
       <c r="B13" t="n">
-        <v>107053</v>
+        <v>107059</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>105107597</v>
       </c>
       <c r="B14" t="n">
-        <v>107053</v>
+        <v>107059</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>105107568</v>
       </c>
       <c r="B15" t="n">
-        <v>107053</v>
+        <v>107059</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>105107588</v>
       </c>
       <c r="B16" t="n">
-        <v>107053</v>
+        <v>107059</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>105107615</v>
       </c>
       <c r="B17" t="n">
-        <v>107053</v>
+        <v>107059</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>105107570</v>
       </c>
       <c r="B18" t="n">
-        <v>107053</v>
+        <v>107059</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>105107572</v>
       </c>
       <c r="B19" t="n">
-        <v>107053</v>
+        <v>107059</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>105107593</v>
       </c>
       <c r="B20" t="n">
-        <v>107053</v>
+        <v>107059</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>105107634</v>
       </c>
       <c r="B21" t="n">
-        <v>107053</v>
+        <v>107059</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>106605053</v>
       </c>
       <c r="B22" t="n">
-        <v>107053</v>
+        <v>107059</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -2046,7 +2046,7 @@
         <v>105107550</v>
       </c>
       <c r="B13" t="n">
-        <v>107059</v>
+        <v>107066</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>105107597</v>
       </c>
       <c r="B14" t="n">
-        <v>107059</v>
+        <v>107066</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>105107568</v>
       </c>
       <c r="B15" t="n">
-        <v>107059</v>
+        <v>107066</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>105107588</v>
       </c>
       <c r="B16" t="n">
-        <v>107059</v>
+        <v>107066</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>105107615</v>
       </c>
       <c r="B17" t="n">
-        <v>107059</v>
+        <v>107066</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>105107570</v>
       </c>
       <c r="B18" t="n">
-        <v>107059</v>
+        <v>107066</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>105107572</v>
       </c>
       <c r="B19" t="n">
-        <v>107059</v>
+        <v>107066</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>105107593</v>
       </c>
       <c r="B20" t="n">
-        <v>107059</v>
+        <v>107066</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>105107634</v>
       </c>
       <c r="B21" t="n">
-        <v>107059</v>
+        <v>107066</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>106605053</v>
       </c>
       <c r="B22" t="n">
-        <v>107059</v>
+        <v>107066</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -2046,7 +2046,7 @@
         <v>105107550</v>
       </c>
       <c r="B13" t="n">
-        <v>107066</v>
+        <v>107070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>105107597</v>
       </c>
       <c r="B14" t="n">
-        <v>107066</v>
+        <v>107070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>105107568</v>
       </c>
       <c r="B15" t="n">
-        <v>107066</v>
+        <v>107070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>105107588</v>
       </c>
       <c r="B16" t="n">
-        <v>107066</v>
+        <v>107070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>105107615</v>
       </c>
       <c r="B17" t="n">
-        <v>107066</v>
+        <v>107070</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>105107570</v>
       </c>
       <c r="B18" t="n">
-        <v>107066</v>
+        <v>107070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>105107572</v>
       </c>
       <c r="B19" t="n">
-        <v>107066</v>
+        <v>107070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>105107593</v>
       </c>
       <c r="B20" t="n">
-        <v>107066</v>
+        <v>107070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>105107634</v>
       </c>
       <c r="B21" t="n">
-        <v>107066</v>
+        <v>107070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>106605053</v>
       </c>
       <c r="B22" t="n">
-        <v>107066</v>
+        <v>107070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -2046,7 +2046,7 @@
         <v>105107550</v>
       </c>
       <c r="B13" t="n">
-        <v>107070</v>
+        <v>107078</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>105107597</v>
       </c>
       <c r="B14" t="n">
-        <v>107070</v>
+        <v>107078</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>105107568</v>
       </c>
       <c r="B15" t="n">
-        <v>107070</v>
+        <v>107078</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>105107588</v>
       </c>
       <c r="B16" t="n">
-        <v>107070</v>
+        <v>107078</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>105107615</v>
       </c>
       <c r="B17" t="n">
-        <v>107070</v>
+        <v>107078</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>105107570</v>
       </c>
       <c r="B18" t="n">
-        <v>107070</v>
+        <v>107078</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>105107572</v>
       </c>
       <c r="B19" t="n">
-        <v>107070</v>
+        <v>107078</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>105107593</v>
       </c>
       <c r="B20" t="n">
-        <v>107070</v>
+        <v>107078</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>105107634</v>
       </c>
       <c r="B21" t="n">
-        <v>107070</v>
+        <v>107078</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>106605053</v>
       </c>
       <c r="B22" t="n">
-        <v>107070</v>
+        <v>107078</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -2046,7 +2046,7 @@
         <v>105107550</v>
       </c>
       <c r="B13" t="n">
-        <v>107081</v>
+        <v>107086</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>105107597</v>
       </c>
       <c r="B14" t="n">
-        <v>107081</v>
+        <v>107086</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>105107568</v>
       </c>
       <c r="B15" t="n">
-        <v>107081</v>
+        <v>107086</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>105107588</v>
       </c>
       <c r="B16" t="n">
-        <v>107081</v>
+        <v>107086</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>105107615</v>
       </c>
       <c r="B17" t="n">
-        <v>107081</v>
+        <v>107086</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>105107570</v>
       </c>
       <c r="B18" t="n">
-        <v>107081</v>
+        <v>107086</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>105107572</v>
       </c>
       <c r="B19" t="n">
-        <v>107081</v>
+        <v>107086</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>105107593</v>
       </c>
       <c r="B20" t="n">
-        <v>107081</v>
+        <v>107086</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>105107634</v>
       </c>
       <c r="B21" t="n">
-        <v>107081</v>
+        <v>107086</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>106605053</v>
       </c>
       <c r="B22" t="n">
-        <v>107081</v>
+        <v>107086</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -2046,7 +2046,7 @@
         <v>105107550</v>
       </c>
       <c r="B13" t="n">
-        <v>107086</v>
+        <v>107094</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>105107597</v>
       </c>
       <c r="B14" t="n">
-        <v>107086</v>
+        <v>107094</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>105107568</v>
       </c>
       <c r="B15" t="n">
-        <v>107086</v>
+        <v>107094</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>105107588</v>
       </c>
       <c r="B16" t="n">
-        <v>107086</v>
+        <v>107094</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>105107615</v>
       </c>
       <c r="B17" t="n">
-        <v>107086</v>
+        <v>107094</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>105107570</v>
       </c>
       <c r="B18" t="n">
-        <v>107086</v>
+        <v>107094</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>105107572</v>
       </c>
       <c r="B19" t="n">
-        <v>107086</v>
+        <v>107094</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>105107593</v>
       </c>
       <c r="B20" t="n">
-        <v>107086</v>
+        <v>107094</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>105107634</v>
       </c>
       <c r="B21" t="n">
-        <v>107086</v>
+        <v>107094</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>106605053</v>
       </c>
       <c r="B22" t="n">
-        <v>107086</v>
+        <v>107094</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>232974</v>
       </c>
       <c r="B2" t="n">
-        <v>88843</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701234.2691078406</v>
+        <v>701234</v>
       </c>
       <c r="R2" t="n">
-        <v>6391419.82371154</v>
+        <v>6391420</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2006-09-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2006-09-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,16 +789,11 @@
         <v>7176464</v>
       </c>
       <c r="B3" t="n">
-        <v>88844</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -851,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701191.4179363601</v>
+        <v>701191</v>
       </c>
       <c r="R3" t="n">
-        <v>6391395.160483933</v>
+        <v>6391395</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -884,19 +864,9 @@
           <t>2014-02-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-02-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -929,37 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16588335</v>
+        <v>16768455</v>
       </c>
       <c r="B4" t="n">
-        <v>88856</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2008</v>
+        <v>682</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Naveljordstjärna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Geastrum elegans</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Vittad.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -979,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701191.4179363601</v>
+        <v>701246</v>
       </c>
       <c r="R4" t="n">
-        <v>6391395.160483933</v>
+        <v>6391425</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,22 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-09-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-09-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,44 +1000,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Dennis Nyström, Elsa Bohus Jensen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17343913</v>
+        <v>17343916</v>
       </c>
       <c r="B5" t="n">
-        <v>88856</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2008</v>
+        <v>682</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Naveljordstjärna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Geastrum elegans</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Vittad.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1094,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701183.8537339279</v>
+        <v>701251</v>
       </c>
       <c r="R5" t="n">
-        <v>6391385.127545295</v>
+        <v>6391437</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1127,19 +1077,9 @@
           <t>2015-04-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-04-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,16 +1110,11 @@
         <v>55822346</v>
       </c>
       <c r="B6" t="n">
-        <v>88844</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1217,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701224.5110247346</v>
+        <v>701225</v>
       </c>
       <c r="R6" t="n">
-        <v>6391421.484465901</v>
+        <v>6391421</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1250,19 +1185,9 @@
           <t>2015-11-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-11-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1295,15 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>55822363</v>
+        <v>105107464</v>
       </c>
       <c r="B7" t="n">
-        <v>88856</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107629</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,39 +1231,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2008</v>
+        <v>1124</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Timjansnyltrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Orobanche alba</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>Stephan ex Willd.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ölbäck, Gtl</t>
+          <t>Ölbäck, V infartskörväg i SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701171.0994781385</v>
+        <v>701168</v>
       </c>
       <c r="R7" t="n">
-        <v>6391403.807295284</v>
+        <v>6391446</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1367,27 +1294,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-11-16</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-07-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-11-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar under en i kanten på stigen.</t>
+          <t>2009-07-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,74 +1308,84 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Torräng vid V-körväg</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56514313</v>
+        <v>105107522</v>
       </c>
       <c r="B8" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>107629</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3215</v>
+        <v>1124</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Timjansnyltrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Orobanche alba</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>Stephan ex Willd.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ölbäck NR, Gtl</t>
+          <t>Ölbäck, ladvägen SV, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701191.4179363601</v>
+        <v>701258</v>
       </c>
       <c r="R8" t="n">
-        <v>6391395.160483933</v>
+        <v>6391413</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1487,27 +1409,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2016-01-14</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-07-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2016-01-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Frystorkade</t>
+          <t>2009-07-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,79 +1423,81 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Åsrygg, SO-kant</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67978565</v>
+        <v>105107550</v>
       </c>
       <c r="B9" t="n">
-        <v>88904</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5735</v>
+        <v>1124</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Timjansnyltrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria broomei</t>
+          <t>Orobanche alba</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Cotton &amp; Wakef.) R.H.Petersen</t>
+          <t>Stephan ex Willd.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Endre, Ölbäck, Gtl</t>
+          <t>Ölbäck, V infartskörväg i SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701161.6256615464</v>
+        <v>701222</v>
       </c>
       <c r="R9" t="n">
-        <v>6391378.121156982</v>
+        <v>6391400</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1615,22 +1524,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-10-16</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-07-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-10-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-07-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,34 +1538,37 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Grusgrop i S</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Dennis Nyström, Magnus Martinsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96781508</v>
+        <v>105107565</v>
       </c>
       <c r="B10" t="n">
-        <v>42591</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107629</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,50 +1576,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101260</v>
+        <v>1124</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Timjansnyltrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Orobanche alba</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Stephan ex Willd.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ölbäck NR, Gtl</t>
+          <t>Ölbäck, ladvägen SV, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701243.8970059552</v>
+        <v>701253</v>
       </c>
       <c r="R10" t="n">
-        <v>6391355.923005602</v>
+        <v>6391390</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1741,22 +1639,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-07-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-07-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1765,87 +1653,84 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Åsrygg, SO-kant</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
+          <t>Projekt Gotlands Flora</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97934797</v>
+        <v>105107566</v>
       </c>
       <c r="B11" t="n">
-        <v>88852</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107629</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4191</v>
+        <v>1124</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Timjansnyltrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Orobanche alba</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>Stephan ex Willd.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ölbäck NR, Gtl</t>
+          <t>Ölbäck, ladvägen SV, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701191.4179363601</v>
+        <v>701270</v>
       </c>
       <c r="R11" t="n">
-        <v>6391395.160483933</v>
+        <v>6391387</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1869,22 +1754,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-07-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-07-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1893,39 +1768,37 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog</t>
+          <t>Kalkhäll och flis i spricksträngar</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103581468</v>
+        <v>105107568</v>
       </c>
       <c r="B12" t="n">
-        <v>44330</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102018</v>
+        <v>1124</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Timjansnyltrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Orobanche alba</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>Stephan ex Willd.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1955,28 +1828,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ölbäck, Gtl</t>
+          <t>Ölbäck, ladvägen SV, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701184.031727773</v>
+        <v>701246</v>
       </c>
       <c r="R12" t="n">
-        <v>6391359.921051381</v>
+        <v>6391384</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2000,22 +1869,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-07-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-07-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Summa 2108 ex på hela Ölbäck</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,29 +1888,37 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Åsrygg, SO-kant</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105107550</v>
+        <v>105107570</v>
       </c>
       <c r="B13" t="n">
-        <v>107094</v>
+        <v>107629</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,7 +1945,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2087,10 +1959,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701222</v>
+        <v>701239</v>
       </c>
       <c r="R13" t="n">
-        <v>6391400</v>
+        <v>6391382</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2125,6 +1997,11 @@
           <t>2009-07-15</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>mot SV frän skyltställ i grusgrop</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2136,7 +2013,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grusgrop i S</t>
+          <t>Körväg och torrbackar</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2158,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105107597</v>
+        <v>105107572</v>
       </c>
       <c r="B14" t="n">
-        <v>107094</v>
+        <v>107629</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2065,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2198,14 +2075,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ölbäck, ladvägen SV, Gtl</t>
+          <t>Ölbäck, V infartskörväg i SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701244</v>
+        <v>701205</v>
       </c>
       <c r="R14" t="n">
-        <v>6391354</v>
+        <v>6391377</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2251,7 +2128,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Åsrygg, SO-kant</t>
+          <t>Torrbacke på åsrygg S-del</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2273,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105107568</v>
+        <v>105107581</v>
       </c>
       <c r="B15" t="n">
-        <v>107094</v>
+        <v>107629</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2180,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2317,10 +2194,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701246</v>
+        <v>701270</v>
       </c>
       <c r="R15" t="n">
-        <v>6391384</v>
+        <v>6391372</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2357,7 +2234,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Summa 2108 ex på hela Ölbäck</t>
+          <t>15 x 3 m i SV-NO</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2371,7 +2248,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Åsrygg, SO-kant</t>
+          <t>Kalkhäll och flis i spricksträngar</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2396,7 +2273,7 @@
         <v>105107588</v>
       </c>
       <c r="B16" t="n">
-        <v>107094</v>
+        <v>107629</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2508,10 +2385,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105107615</v>
+        <v>105107593</v>
       </c>
       <c r="B17" t="n">
-        <v>107094</v>
+        <v>107629</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2415,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2548,14 +2425,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ölbäck 200 m SSV, Gtl</t>
+          <t>Ölbäck, ladvägen SV, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701230</v>
+        <v>701247</v>
       </c>
       <c r="R17" t="n">
-        <v>6391342</v>
+        <v>6391362</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2582,12 +2459,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>1998-07-14</t>
+          <t>2009-07-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1998-07-14</t>
+          <t>2009-07-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2601,7 +2478,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Grusås vid körväg.</t>
+          <t>Åsrygg, SO-kant</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2623,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105107570</v>
+        <v>105107597</v>
       </c>
       <c r="B18" t="n">
-        <v>107094</v>
+        <v>107629</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2653,7 +2530,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2663,14 +2540,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ölbäck, V infartskörväg i SV-del, Gtl</t>
+          <t>Ölbäck, ladvägen SV, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701239</v>
+        <v>701244</v>
       </c>
       <c r="R18" t="n">
-        <v>6391382</v>
+        <v>6391354</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2705,11 +2582,6 @@
           <t>2009-07-15</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>mot SV frän skyltställ i grusgrop</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2721,7 +2593,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Körväg och torrbackar</t>
+          <t>Åsrygg, SO-kant</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2743,10 +2615,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>105107572</v>
+        <v>105107615</v>
       </c>
       <c r="B19" t="n">
-        <v>107094</v>
+        <v>107629</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,7 +2645,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2783,14 +2655,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ölbäck, V infartskörväg i SV-del, Gtl</t>
+          <t>Ölbäck 200 m SSV, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701205</v>
+        <v>701230</v>
       </c>
       <c r="R19" t="n">
-        <v>6391377</v>
+        <v>6391342</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2817,12 +2689,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2009-07-15</t>
+          <t>1998-07-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2009-07-15</t>
+          <t>1998-07-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2836,7 +2708,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Torrbacke på åsrygg S-del</t>
+          <t>Grusås vid körväg.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2858,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105107593</v>
+        <v>105107634</v>
       </c>
       <c r="B20" t="n">
-        <v>107094</v>
+        <v>107629</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2888,7 +2760,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2898,14 +2770,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ölbäck, ladvägen SV, Gtl</t>
+          <t>Ölbäck 350 m SSV, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701247</v>
+        <v>701230</v>
       </c>
       <c r="R20" t="n">
-        <v>6391362</v>
+        <v>6391332</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2932,12 +2804,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2009-07-15</t>
+          <t>1994-08-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2009-07-15</t>
+          <t>1994-08-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ca 40 ex. Tidigare känd lokal.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2951,7 +2828,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Åsrygg, SO-kant</t>
+          <t>Torrbacke.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2973,10 +2850,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>105107634</v>
+        <v>106605053</v>
       </c>
       <c r="B21" t="n">
-        <v>107094</v>
+        <v>107629</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3001,23 +2878,14 @@
           <t>Stephan ex Willd.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ölbäck 350 m SSV, Gtl</t>
+          <t>Ölbäck, ca 300 m SSV P-plats, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701230</v>
+        <v>701210</v>
       </c>
       <c r="R21" t="n">
         <v>6391332</v>
@@ -3047,17 +2915,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>1994-08-08</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1994-08-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ca 40 ex. Tidigare känd lokal.</t>
+          <t>1992-12-31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3068,11 +2931,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Torrbacke.</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3082,7 +2940,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Torgny Rosvall</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3093,10 +2951,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>106605053</v>
+        <v>16588335</v>
       </c>
       <c r="B22" t="n">
-        <v>107094</v>
+        <v>91333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3104,37 +2962,47 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1124</v>
+        <v>2008</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Timjansnyltrot</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Orobanche alba</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Stephan ex Willd.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ölbäck, ca 300 m SSV P-plats, Gtl</t>
+          <t>Ölbäck NR, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>701210</v>
+        <v>701191</v>
       </c>
       <c r="R22" t="n">
-        <v>6391332</v>
+        <v>6391395</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3158,12 +3026,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>2014-09-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1992-12-31</t>
+          <t>2014-09-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3172,37 +3040,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Torgny Rosvall</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>106643595</v>
+        <v>17343913</v>
       </c>
       <c r="B23" t="n">
-        <v>88856</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3224,34 +3084,25 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Endre, Ölbäck, Gtl</t>
+          <t>Ölbäck, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>701161.6256615464</v>
+        <v>701184</v>
       </c>
       <c r="R23" t="n">
-        <v>6391378.121156982</v>
+        <v>6391385</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3275,22 +3126,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-02-02</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-02-02</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3306,27 +3147,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Michael Tholin, Dennis Nyström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118098657</v>
+        <v>55822363</v>
       </c>
       <c r="B24" t="n">
-        <v>44525</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3334,54 +3170,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102018</v>
+        <v>2008</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stadshajden, Gtl</t>
+          <t>Ölbäck, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>701186</v>
+        <v>701171</v>
       </c>
       <c r="R24" t="n">
-        <v>6391366</v>
+        <v>6391404</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3405,22 +3226,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2015-11-16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2015-11-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar under en i kanten på stigen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3429,71 +3245,77 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Peter Olofsson</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Peter Olofsson, Evelina Lindgren</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120661706</v>
+        <v>56212174</v>
       </c>
       <c r="B25" t="n">
-        <v>86174</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>248956</v>
+        <v>2008</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stadshajden, Stadshajden, Gtl</t>
+          <t>Ölbäck, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>701191</v>
+        <v>701172</v>
       </c>
       <c r="R25" t="n">
-        <v>6391369</v>
+        <v>6391404</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3517,12 +3339,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2015-12-22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2015-12-22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3531,68 +3353,75 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Törnvall</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Törnvall</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120661712</v>
+        <v>106643595</v>
       </c>
       <c r="B26" t="n">
-        <v>89329</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>245042</v>
+        <v>2008</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stadshajden, Stadshajden, Gtl</t>
+          <t>Endre, Ölbäck, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>701227</v>
+        <v>701162</v>
       </c>
       <c r="R26" t="n">
-        <v>6391428</v>
+        <v>6391378</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3619,12 +3448,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3633,21 +3462,2116 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>106605052</v>
+      </c>
+      <c r="B27" t="n">
+        <v>102864</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2078</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gråfingerört</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Potentilla incana</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>G. Gaertn., B. Mey. &amp; Scherb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ölbäck, ca 350 m S P-plats, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>701270</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6391302</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>1988-01-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1992-12-31</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Torgny Rosvall</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>56514313</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91680</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ölbäck NR, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>701191</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6391395</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2016-01-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2016-01-14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Frystorkade</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>97934797</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91329</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4191</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Geastrum michelianum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Berk. &amp; Broome</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ölbäck NR, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>701191</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6391395</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-01-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-01-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>67978565</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91382</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5735</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Svartnande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phaeoclavulina macrospora</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Brinkmann</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Endre, Ölbäck, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>701162</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6391378</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2017-10-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2017-10-16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Dennis Nyström, Magnus Martinsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>89011971</v>
+      </c>
+      <c r="B31" t="n">
+        <v>43299</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>101260</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svartfläckig blåvinge</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phengaris arion</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ölbäck NR, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>701186</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6391315</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2020-07-25</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2020-07-25</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>96781501</v>
+      </c>
+      <c r="B32" t="n">
+        <v>43299</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>101260</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svartfläckig blåvinge</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phengaris arion</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ölbäck NR, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>701271</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6391399</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>96781504</v>
+      </c>
+      <c r="B33" t="n">
+        <v>43299</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>101260</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svartfläckig blåvinge</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phengaris arion</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ölbäck NR, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>701262</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6391375</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>96781508</v>
+      </c>
+      <c r="B34" t="n">
+        <v>43299</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>101260</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Svartfläckig blåvinge</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phengaris arion</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ölbäck NR, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>701244</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6391356</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>96781601</v>
+      </c>
+      <c r="B35" t="n">
+        <v>43299</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>101260</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Svartfläckig blåvinge</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phengaris arion</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ölbäck NR, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>701203</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6391325</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>96781606</v>
+      </c>
+      <c r="B36" t="n">
+        <v>43299</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>101260</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Svartfläckig blåvinge</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phengaris arion</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ölbäck NR, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>701254</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6391306</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>103581402</v>
+      </c>
+      <c r="B37" t="n">
+        <v>43299</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>101260</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svartfläckig blåvinge</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phengaris arion</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ölbäck, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>701257</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6391380</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>111187561</v>
+      </c>
+      <c r="B38" t="n">
+        <v>43299</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>101260</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Svartfläckig blåvinge</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phengaris arion</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ölbäck, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>701267</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6391406</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129320440</v>
+      </c>
+      <c r="B39" t="n">
+        <v>43299</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>101260</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svartfläckig blåvinge</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Phengaris arion</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ölbäck, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>701274</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6391375</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>103581468</v>
+      </c>
+      <c r="B40" t="n">
+        <v>45044</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>102018</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Zygaena lonicerae</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ölbäck, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>701184</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6391360</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>118098657</v>
+      </c>
+      <c r="B41" t="n">
+        <v>45044</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>102018</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Zygaena lonicerae</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stadshajden, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>701186</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6391366</v>
+      </c>
+      <c r="S41" t="n">
+        <v>11</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Peter Olofsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Peter Olofsson, Evelina Lindgren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>61244250</v>
+      </c>
+      <c r="B42" t="n">
+        <v>102225</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ölbäcks naturreservat, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>701253</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6391419</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2016-08-22</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2016-08-22</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Elin Götmark, Linnea Helmersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>106605049</v>
+      </c>
+      <c r="B43" t="n">
+        <v>102225</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ölbäck, ca 400 m SSV P-plats, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>701100</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6391270</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>1988-01-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>1992-12-31</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Torgny Rosvall</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120661712</v>
+      </c>
+      <c r="B44" t="n">
+        <v>90665</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stadshajden, Stadshajden, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>701227</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6391428</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
+      <c r="AX44" t="inlineStr">
         <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120661706</v>
+      </c>
+      <c r="B45" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stadshajden, Stadshajden, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>701191</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6391369</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5183,48 +5183,65 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>61244250</v>
+        <v>135246965</v>
       </c>
       <c r="B42" t="n">
-        <v>102225</v>
+        <v>45050</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221223</v>
+        <v>102018</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ölbäcks naturreservat, Gtl</t>
+          <t>Stadshajden, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701253</v>
+        <v>701159</v>
       </c>
       <c r="R42" t="n">
         <v>6391419</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5248,12 +5265,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2016-08-22</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2016-08-22</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5268,19 +5295,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Edvin Klein</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Götmark, Linnea Helmersson</t>
+          <t>Edvin Klein, Musse Björklund</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>106605049</v>
+        <v>61244250</v>
       </c>
       <c r="B43" t="n">
         <v>102225</v>
@@ -5311,14 +5338,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ölbäck, ca 400 m SSV P-plats, Gtl</t>
+          <t>Ölbäcks naturreservat, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701100</v>
+        <v>701253</v>
       </c>
       <c r="R43" t="n">
-        <v>6391270</v>
+        <v>6391419</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5345,12 +5372,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>2016-08-22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>1992-12-31</t>
+          <t>2016-08-22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5365,61 +5392,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Torgny Rosvall</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Elin Götmark, Linnea Helmersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120661712</v>
+        <v>106605049</v>
       </c>
       <c r="B44" t="n">
-        <v>90665</v>
+        <v>102225</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>245042</v>
+        <v>221223</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stadshajden, Stadshajden, Gtl</t>
+          <t>Ölbäck, ca 400 m SSV P-plats, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701227</v>
+        <v>701100</v>
       </c>
       <c r="R44" t="n">
-        <v>6391428</v>
+        <v>6391270</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5446,12 +5469,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>1992-12-31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5466,44 +5489,48 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Torgny Rosvall</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120661706</v>
+        <v>120661712</v>
       </c>
       <c r="B45" t="n">
-        <v>87262</v>
+        <v>90665</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>248956</v>
+        <v>245042</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5513,10 +5540,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>701191</v>
+        <v>701227</v>
       </c>
       <c r="R45" t="n">
-        <v>6391369</v>
+        <v>6391428</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5572,6 +5599,103 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120661706</v>
+      </c>
+      <c r="B46" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stadshajden, Stadshajden, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>701191</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6391369</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/232974</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7176464</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16768455</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17343916</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55822346</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105107464</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105107522</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1562,6 +1602,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105107550</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1677,6 +1722,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105107565</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105107566</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1912,6 +1967,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105107568</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2032,6 +2092,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105107570</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2147,6 +2212,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105107572</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2267,6 +2337,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105107581</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2382,6 +2457,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105107588</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2497,6 +2577,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105107593</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2612,6 +2697,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105107597</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2727,6 +2817,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105107615</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2847,6 +2942,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105107634</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2948,6 +3048,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106605053</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3056,6 +3161,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16588335</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3156,6 +3266,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17343913</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3261,6 +3376,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55822363</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3369,6 +3489,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56212174</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3478,6 +3603,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106643595</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3579,6 +3709,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106605052</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3684,6 +3819,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56514313</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3798,6 +3938,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97934797</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3906,6 +4051,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67978565</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4025,6 +4175,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89011971</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4140,6 +4295,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96781501</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4255,6 +4415,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96781504</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4370,6 +4535,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96781508</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4485,6 +4655,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96781601</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4600,6 +4775,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96781606</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4715,6 +4895,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103581402</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4830,6 +5015,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111187561</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4945,6 +5135,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129320440</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5056,6 +5251,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103581468</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5180,6 +5380,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118098657</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5304,6 +5509,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135246965</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5401,6 +5611,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61244250</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5502,6 +5717,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106605049</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5599,6 +5819,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120661712</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5696,8 +5921,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120661706</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -5391,7 +5391,7 @@
         <v>135246965</v>
       </c>
       <c r="B42" t="n">
-        <v>45050</v>
+        <v>45055</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ45"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5388,48 +5388,65 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>61244250</v>
+        <v>135246965</v>
       </c>
       <c r="B42" t="n">
-        <v>102225</v>
+        <v>45055</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221223</v>
+        <v>102018</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ölbäcks naturreservat, Gtl</t>
+          <t>Stadshajden, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701253</v>
+        <v>701159</v>
       </c>
       <c r="R42" t="n">
         <v>6391419</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5453,12 +5470,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2016-08-22</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2016-08-22</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5473,24 +5500,24 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Edvin Klein</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Götmark, Linnea Helmersson</t>
+          <t>Edvin Klein, Musse Björklund</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61244250</t>
+          <t>https://artportalen.se/Sighting/135246965</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>106605049</v>
+        <v>61244250</v>
       </c>
       <c r="B43" t="n">
         <v>102225</v>
@@ -5521,14 +5548,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ölbäck, ca 400 m SSV P-plats, Gtl</t>
+          <t>Ölbäcks naturreservat, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701100</v>
+        <v>701253</v>
       </c>
       <c r="R43" t="n">
-        <v>6391270</v>
+        <v>6391419</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5555,12 +5582,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>2016-08-22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>1992-12-31</t>
+          <t>2016-08-22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5575,66 +5602,62 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Torgny Rosvall</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Elin Götmark, Linnea Helmersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106605049</t>
+          <t>https://artportalen.se/Sighting/61244250</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120661712</v>
+        <v>106605049</v>
       </c>
       <c r="B44" t="n">
-        <v>90665</v>
+        <v>102225</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>245042</v>
+        <v>221223</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stadshajden, Stadshajden, Gtl</t>
+          <t>Ölbäck, ca 400 m SSV P-plats, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701227</v>
+        <v>701100</v>
       </c>
       <c r="R44" t="n">
-        <v>6391428</v>
+        <v>6391270</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5661,12 +5684,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>1992-12-31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5681,49 +5704,53 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Torgny Rosvall</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120661712</t>
+          <t>https://artportalen.se/Sighting/106605049</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120661706</v>
+        <v>120661712</v>
       </c>
       <c r="B45" t="n">
-        <v>87262</v>
+        <v>90665</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>248956</v>
+        <v>245042</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5733,10 +5760,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>701191</v>
+        <v>701227</v>
       </c>
       <c r="R45" t="n">
-        <v>6391369</v>
+        <v>6391428</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5793,6 +5820,108 @@
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120661712</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120661706</v>
+      </c>
+      <c r="B46" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stadshajden, Stadshajden, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>701191</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6391369</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120661706</t>
         </is>
@@ -5844,6 +5973,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
